--- a/data/raw/inventory/Week 27/Audio_Array/Inventory Snapshot.xlsx
+++ b/data/raw/inventory/Week 27/Audio_Array/Inventory Snapshot.xlsx
@@ -1314,7 +1314,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L245"/>
+  <dimension ref="A1:L250"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="12.88671875" bestFit="1" customWidth="1" style="1" min="1" max="1"/>
@@ -8667,8 +8667,216 @@
       </c>
       <c r="K243" s="8" t="n"/>
     </row>
-    <row r="244" ht="15" customHeight="1"/>
-    <row r="245" ht="15" customHeight="1"/>
+    <row r="244" ht="15" customHeight="1">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>FBA76597</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>B0BQ7H7418</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>Audio Array</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>AA-06</t>
+        </is>
+      </c>
+      <c r="I244" t="n">
+        <v>2</v>
+      </c>
+      <c r="J244" t="inlineStr">
+        <is>
+          <t>AMPM</t>
+        </is>
+      </c>
+    </row>
+    <row r="245" ht="15" customHeight="1">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>FBA79005</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>B0CKHVHVQ1</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>Audio Array</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>AM-W45</t>
+        </is>
+      </c>
+      <c r="I245" t="n">
+        <v>408</v>
+      </c>
+      <c r="J245" t="inlineStr">
+        <is>
+          <t>AMPM</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>FBA79105</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>B0CM6WH4ZT</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>Audio Array</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>AI-12</t>
+        </is>
+      </c>
+      <c r="I246" t="n">
+        <v>998</v>
+      </c>
+      <c r="J246" t="inlineStr">
+        <is>
+          <t>AMPM</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>FBA79962</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>B0G53LZNY3</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>Audio Array</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>BE-4T</t>
+        </is>
+      </c>
+      <c r="I247" t="n">
+        <v>170</v>
+      </c>
+      <c r="J247" t="inlineStr">
+        <is>
+          <t>AMPM</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>FBA79966</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>B0G53KWRVW</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>Audio Array</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>AM-Mix10</t>
+        </is>
+      </c>
+      <c r="I248" t="n">
+        <v>7</v>
+      </c>
+      <c r="J248" t="inlineStr">
+        <is>
+          <t>AMPM</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>FBA80013</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>B0GTZLGPFR</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>Audio Array</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>XM-16</t>
+        </is>
+      </c>
+      <c r="I249" t="n">
+        <v>2</v>
+      </c>
+      <c r="J249" t="inlineStr">
+        <is>
+          <t>AMPM</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>FBA80085</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>B0GXPBHDRF</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>Audio Array</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>M6</t>
+        </is>
+      </c>
+      <c r="I250" t="n">
+        <v>222</v>
+      </c>
+      <c r="J250" t="inlineStr">
+        <is>
+          <t>AMPM</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:L243"/>
   <conditionalFormatting sqref="A129">
